--- a/ig/main/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/main/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2025-04-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Caractérise le statut du processus d'évaluation de l'autonomie de l'usager par un professionnel de santé ou par lui-même lors d'une auto évaluation</t>
+    <t>Caractérise le statut d'une ressource du médico-social au cours de son cycle de vie</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -169,34 +169,97 @@
     <t>Terminé</t>
   </si>
   <si>
+    <t>La ressource est totalement finie. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS. Resource achevée. Ce statut s'adresse au projet personnalisé ainsi qu'à ses ressources Action et Objectif.</t>
+  </si>
+  <si>
     <t>VALIDE</t>
   </si>
   <si>
     <t>Validé</t>
   </si>
   <si>
+    <t>Ressource approuvée officiellement par un tiers comme le personnel de santé. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+  </si>
+  <si>
     <t>APPROUVE</t>
   </si>
   <si>
     <t>Approuvé</t>
   </si>
   <si>
+    <t>Le professionnel considère la ressource comme correcte. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+  </si>
+  <si>
     <t>PLANIFIE</t>
   </si>
   <si>
     <t>Planifié</t>
   </si>
   <si>
+    <t>Organiser une activité à l'avance.Ce statut s'adresse aux ressources Evaluation et Evenement</t>
+  </si>
+  <si>
     <t>REALISE</t>
   </si>
   <si>
     <t>Réalisé</t>
   </si>
   <si>
+    <t>Resoource totalement effectuée. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS.</t>
+  </si>
+  <si>
     <t>ANNULE</t>
   </si>
   <si>
     <t>Annulé</t>
+  </si>
+  <si>
+    <t>La ressource est supprimée. Ce statut s'adresse aux ressources Evaluation de l'individu et Evenements liés à la prise en charge de l'individu dans une structure ESSMS</t>
+  </si>
+  <si>
+    <t>ACTIF</t>
+  </si>
+  <si>
+    <t>Actif</t>
+  </si>
+  <si>
+    <t>Ressource vivante. Ce statut s'adresse aux ressources du projet personnalisé Action et Objectif.</t>
+  </si>
+  <si>
+    <t>NONDEBUTE</t>
+  </si>
+  <si>
+    <t>Non débuté</t>
+  </si>
+  <si>
+    <t>Ressource qui n'a pas commencée. Ce statut s'adresse projet personnalisé.</t>
+  </si>
+  <si>
+    <t>ENPREPARATION</t>
+  </si>
+  <si>
+    <t>En préparation</t>
+  </si>
+  <si>
+    <t>Ressource qui est en train d'être faite, conçue, élaborée. Ce statut s'adresse au projet personnalisé.</t>
+  </si>
+  <si>
+    <t>ENREALISATION</t>
+  </si>
+  <si>
+    <t>En réalisation</t>
+  </si>
+  <si>
+    <t>Ressource qui est en cours d'élaboration. Ce statut s'adresse au projet personnalisé</t>
+  </si>
+  <si>
+    <t>CREATION</t>
+  </si>
+  <si>
+    <t>Création</t>
+  </si>
+  <si>
+    <t>Etat de la ressource après la préparation. Ce statut s'adresse au projet personnalisé</t>
   </si>
 </sst>
 </file>
@@ -566,7 +629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -593,67 +656,149 @@
       <c r="C2" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
         <v>48</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-TRE-R368-StatutRessource.xlsx
+++ b/ig/main/CodeSystem-TRE-R368-StatutRessource.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:oid:1.2.250.1.213.3.3.250</t>
+    <t>OID:1.2.250.1.213.3.3.250</t>
   </si>
   <si>
     <t>Version</t>
@@ -43,7 +43,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>TRE_R368-StatutRessource</t>
+    <t>TRE_R368_StatutRessource</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,6 +58,9 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -149,6 +152,36 @@
   </si>
   <si>
     <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
   </si>
   <si>
     <t>Level</t>
@@ -458,107 +491,111 @@
       <c r="A8" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2"/>
     </row>
@@ -569,57 +606,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -634,170 +713,170 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
